--- a/artfynd/A 61984-2025 artfynd.xlsx
+++ b/artfynd/A 61984-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87607602</v>
+        <v>3330943</v>
       </c>
       <c r="B2" t="n">
-        <v>103088</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,17 +706,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>körväg NV om Hjortis, Vg</t>
+          <t>Traktorväg i fuktig skog, Martinamarka, Naglarp, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410059.1145736598</v>
+        <v>409996</v>
       </c>
       <c r="R2" t="n">
-        <v>6438056.407222815</v>
+        <v>6438305</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-05-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-05-29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2 ex; spridd i trakten, från vår trädgård</t>
+          <t>rikligt i traktorvägen och i skogskanten vid ledet (och även vid Brodda). Säkerligen spridd från odling i trädgården.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -789,6 +774,219 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>87607602</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106061</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>körväg NV om Hjortis, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>410059</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6438056</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kinneved</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-07-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-07-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 ex; spridd i trakten, från vår trädgård</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4284301</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Villemaden, Naglarp, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>410016</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6437868</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kinneved</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1986-06-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1986-06-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 blommande + 1 icke-blommande planta på [lilla] ön i vitmossa</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
